--- a/data/trans_camb/IP1003-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-2.866110482023992</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.456026755106647</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.54402991436197</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.606785363077851</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-2.224684658509679</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1.544967451975451</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-6.12718548263353</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.036419088913326</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.910153942327826</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.151434481258163</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-4.502660172651387</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.066833423637905</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>0.4740887540854281</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.667442325458353</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.611217190603477</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.832516263303792</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.07920830047087329</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>6.183798596501749</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.4387291781627607</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.2228809481202627</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.2800453751275049</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.2914275206503759</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3686065473315585</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2559846475472193</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.7147187217227812</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.4085751205030704</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.6448036770516925</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.5153475828489122</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6077092960432654</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3102534731222823</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.1112668579684516</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1.688881328152918</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.4809956278683606</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1.901181796782133</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.04162438962006064</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.199829171907862</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-2.22054415024583</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.2110236769096538</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.857920327059438</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.5340302532004806</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.176146410140781</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.5078674496897896</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-6.363514123123101</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.254702056676744</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.453720212451383</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.133106803825818</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.693325648558095</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-2.581680227709585</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>2.089170418091209</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.066268649859333</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.353363596931705</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.097785127876953</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.350448194342084</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>3.376001197931799</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.2678753660935785</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.02545684340495031</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.5393748626461297</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.1550349012676862</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.03004399929822253</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.08662322036466824</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.594769061211361</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.4211182083644021</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.3282205523324612</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.4962540453490418</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3951333816638836</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3672124543641237</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.3990941553308303</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.9664521367239413</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2.647525157411802</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2.197659717722068</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5219799443902015</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7151748844733653</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>1.711362611622129</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4.267146827567786</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1741901946670191</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.870396146412503</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.942935366551037</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>3.605155759983381</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-2.204703436913249</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1101175262836289</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.587952443434499</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.675338404461479</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.873606056940258</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.3507798059191384</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>6.474761383149695</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>9.026740414268669</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.361788648080739</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.445578414940019</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>3.982488531192551</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>6.908371179878483</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.4162117358998526</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1.037790925418258</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.03527238498307582</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.581236608201396</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.208729989181544</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.7980442238915454</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.4237786197911409</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.03769394683557821</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.5402019580473391</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.274237706247733</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.330583064200834</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.01256054242689091</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>2.728193262487677</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3.507944301384641</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1.629343452678121</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>2.431095415684135</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1.242015019177935</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2.091805464513405</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>3.591141448270208</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4.710445178689554</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-2.207839429359354</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.23973367688781</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.018060323090369</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>2.395501756220401</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-1.701878835301978</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.08278718630038343</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-9.426126893012391</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-7.134772535243726</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-3.429587834920062</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-1.402741918274466</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>8.88370388542687</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>9.891937456934841</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.987585095418004</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>5.258355361626047</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>4.924221877035972</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>6.17649325510253</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>1.018114627142733</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>1.33544534679575</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.3490463338629086</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.03790047406003886</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.2128278343452988</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.5007851100602145</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.3722364872260847</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.1755318632285874</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.916766063118754</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.689376254432488</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.5359168375907344</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.2489996728490482</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>6.366604800140709</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>6.101647123484067</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>2.01452759761955</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1.894778204315826</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1.81546699577778</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>2.347214542355167</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.9056307359187263</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>2.199050953471657</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.1976801717992624</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1.299391454080622</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.5585732024579744</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1.802621456641668</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-3.010724291707033</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-0.03827108394767696</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-1.952607049051033</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-1.019689571067707</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.041526720317377</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.1425094713288071</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>1.051720311879164</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>4.815351735762281</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.772445110100043</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>3.538496469929546</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.7735877049808427</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>3.561908398294179</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.147694181278019</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.3586307501281524</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.04100444899988234</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.269530475033362</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.1016983627361512</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.3281998670305106</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.402908579161865</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.02990782744504812</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.3371376873000989</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.1818832408292505</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.3235902323728571</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.02140762464879376</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.2033015685932014</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.8720415549368153</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.4610725681679674</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.9019749826992033</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.1628667142346853</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.7217385568353382</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
